--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_xgb_yearly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_xgb_yearly.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -917,27 +918,27 @@
         <v>1.07421834762458</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF3" s="3" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>4/7</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>4/6</t>
-        </is>
-      </c>
-      <c r="AH3" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>3/5</t>
         </is>
       </c>
       <c r="AJ3" s="3" t="inlineStr"/>
@@ -1040,27 +1041,27 @@
         <v>0.8699837092823588</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AJ4" s="3" t="n">
@@ -1068,7 +1069,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AL4" s="3" t="n">
@@ -1076,15 +1077,15 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr"/>
@@ -1189,51 +1190,51 @@
         <v>0.4517589417296295</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AP5" s="3" t="inlineStr"/>
@@ -1342,75 +1343,75 @@
         <v>0.8839346550209342</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AP6" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AR6" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AT6" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
     </row>
@@ -1509,51 +1510,51 @@
         <v>1.035202730925826</v>
       </c>
       <c r="AD7" s="3" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2/7</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>4/7</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>2/7</t>
+        </is>
+      </c>
+      <c r="AL7" s="3" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>2/7</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>2/6</t>
-        </is>
-      </c>
-      <c r="AF7" s="3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="AH7" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>2/5</t>
-        </is>
-      </c>
-      <c r="AJ7" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AL7" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AN7" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>2/5</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr"/>
@@ -1662,75 +1663,75 @@
         <v>1.035202730925826</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH8" s="3" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="AP8" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AR8" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AT8" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
     </row>
@@ -1829,51 +1830,51 @@
         <v>0.8819508042981035</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH9" s="3" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
+      <c r="AL9" s="3" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AK9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>4/6</t>
-        </is>
-      </c>
-      <c r="AL9" s="3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="AN9" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>3/5</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr"/>
@@ -1982,75 +1983,75 @@
         <v>1.049495772959609</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH10" s="3" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AN10" s="3" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="AP10" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AR10" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AT10" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
     </row>
@@ -2349,66 +2350,68 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>36116</v>
+      </c>
       <c r="M2" t="n">
-        <v>1896</v>
+        <v>86</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>-0.4859401977791227</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>-0.4862309442441404</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="P2" t="n">
-        <v>1895</v>
+        <v>85</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.2657575172078715</v>
+        <v>0.09032004823014485</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.2657575172078715</v>
+        <v>0.04076898034342919</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="b">
-        <v>1</v>
-      </c>
-      <c r="V2" s="3" t="n">
-        <v>-0.03939252582908814</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X2" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.4859401977791227</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.4862309442441404</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1313</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.9452989626493449</v>
+        <v>0.204425521991354</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -2456,66 +2459,68 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>37538</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>36115</v>
+      </c>
       <c r="M3" t="n">
-        <v>1896</v>
+        <v>85</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-0.5046718081597298</v>
+        <v>-0.1801116697737415</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.5086484580604441</v>
+        <v>-0.1858856338605598</v>
       </c>
       <c r="P3" t="n">
-        <v>1894</v>
+        <v>83</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.2788179371039247</v>
+        <v>0.1002859776838859</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.2788179371039247</v>
+        <v>0.04500652696670188</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
       </c>
       <c r="U3" t="b">
-        <v>1</v>
-      </c>
-      <c r="V3" s="3" t="n">
-        <v>-0.02190491807181505</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>638</v>
+        <v>31</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.5046718081597298</v>
+        <v>-0.1801116697737415</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.5086484580604441</v>
+        <v>-0.1858856338605598</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1258</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-1</v>
+      </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>1.018863485812802</v>
+        <v>0.2196782941452984</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -2523,9 +2528,11 @@
       <c r="AG3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr"/>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
       <c r="AI3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ3" s="3" t="inlineStr"/>
       <c r="AK3" s="3" t="inlineStr"/>
@@ -2569,34 +2576,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>38028</v>
+        <v>36105</v>
       </c>
       <c r="M4" t="n">
-        <v>975</v>
+        <v>79</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.2967359307877762</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="P4" t="n">
-        <v>786</v>
+        <v>78</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1468876731549894</v>
+        <v>0.08993390447450868</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.1053602020059354</v>
+        <v>0.03892731995262652</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -2606,39 +2613,43 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X4" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2967359307877762</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>392</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-7</v>
+      </c>
       <c r="AD4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.4219409803207652</v>
+        <v>0.1946904599376615</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.1734577350979893</v>
+        <v>-0.006079207014075362</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.2079358773719536</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
+        <v>0.01714857057244679</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-6</v>
+      </c>
       <c r="AI4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" s="3" t="inlineStr"/>
       <c r="AK4" s="3" t="inlineStr"/>
@@ -2690,34 +2701,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>36893</v>
+        <v>36038</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>39094</v>
+        <v>36115</v>
       </c>
       <c r="M5" t="n">
-        <v>1710</v>
+        <v>85</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.2084679878443056</v>
+        <v>-0.1801116697737415</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.2148226548093675</v>
+        <v>-0.1858856338605598</v>
       </c>
       <c r="P5" t="n">
-        <v>1707</v>
+        <v>83</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.1623322432620348</v>
+        <v>0.1002859776838859</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.1541686713193326</v>
+        <v>0.04500652696670188</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -2727,39 +2738,43 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>196</v>
+        <v>31</v>
       </c>
       <c r="X5" t="n">
-        <v>-442</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.2084679878443056</v>
+        <v>-0.1801116697737415</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.2148226548093675</v>
+        <v>-0.1858856338605598</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1514</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-1</v>
+      </c>
       <c r="AD5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.2633727816978044</v>
+        <v>0.2196782941452984</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.1246492657845921</v>
+        <v>0</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.2962038203154241</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
       <c r="AI5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ5" s="3" t="inlineStr"/>
       <c r="AK5" s="3" t="inlineStr"/>
@@ -2815,34 +2830,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>39218</v>
+        <v>36115</v>
       </c>
       <c r="M6" t="n">
-        <v>1795</v>
+        <v>85</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.447940300526473</v>
+        <v>-0.1801116697737415</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.4523724087433373</v>
+        <v>-0.1858856338605598</v>
       </c>
       <c r="P6" t="n">
-        <v>1792</v>
+        <v>83</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.2362632872251003</v>
+        <v>0.1002859776838859</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.2298877040605186</v>
+        <v>0.04500652696670188</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -2852,48 +2867,52 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X6" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.447940300526473</v>
+        <v>-0.1801116697737415</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.4523724087433373</v>
+        <v>-0.1858856338605598</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1212</v>
-      </c>
-      <c r="AC6" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-1</v>
+      </c>
       <c r="AD6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.8113982979624348</v>
+        <v>0.2196782941452984</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.04893023304340613</v>
+        <v>0</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.05673150763325674</v>
-      </c>
-      <c r="AH6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
       <c r="AI6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.1245275020545831</v>
+        <v>0.006079207014075362</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.1512043697386969</v>
+        <v>-0.01714857057244679</v>
       </c>
       <c r="AL6" t="n">
-        <v>820</v>
+        <v>6</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
@@ -2944,66 +2963,68 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>37538</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>36115</v>
+      </c>
       <c r="M7" t="n">
-        <v>1896</v>
+        <v>85</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.5046718081597298</v>
+        <v>-0.1801116697737415</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.5086484580604441</v>
+        <v>-0.1858856338605598</v>
       </c>
       <c r="P7" t="n">
-        <v>1894</v>
+        <v>83</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.2788179371039247</v>
+        <v>0.1002859776838859</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.2788179371039247</v>
+        <v>0.04500652696670188</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>1</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>-0.02190491807181505</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>638</v>
+        <v>31</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.5046718081597298</v>
+        <v>-0.1801116697737415</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.5086484580604441</v>
+        <v>-0.1858856338605598</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1258</v>
-      </c>
-      <c r="AC7" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-1</v>
+      </c>
       <c r="AD7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>1.018863485812802</v>
+        <v>0.2196782941452984</v>
       </c>
       <c r="AF7" s="3" t="n">
         <v>0</v>
@@ -3011,9 +3032,11 @@
       <c r="AG7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr"/>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
       <c r="AI7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
       <c r="AK7" s="3" t="inlineStr"/>
@@ -3069,66 +3092,68 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>37538</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>36115</v>
+      </c>
       <c r="M8" t="n">
-        <v>1896</v>
+        <v>85</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.5046718081597298</v>
+        <v>-0.1801116697737415</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.5086484580604441</v>
+        <v>-0.1858856338605598</v>
       </c>
       <c r="P8" t="n">
-        <v>1894</v>
+        <v>83</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.2788179371039247</v>
+        <v>0.1002859776838859</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.2788179371039247</v>
+        <v>0.04500652696670188</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>1</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>-0.02190491807181505</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>638</v>
+        <v>31</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.5046718081597298</v>
+        <v>-0.1801116697737415</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.5086484580604441</v>
+        <v>-0.1858856338605598</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1258</v>
-      </c>
-      <c r="AC8" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-1</v>
+      </c>
       <c r="AD8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>1.018863485812802</v>
+        <v>0.2196782941452984</v>
       </c>
       <c r="AF8" s="3" t="n">
         <v>0</v>
@@ -3136,19 +3161,23 @@
       <c r="AG8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr"/>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
       <c r="AI8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.1734577350979893</v>
+        <v>0.006079207014075362</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.2079358773719536</v>
-      </c>
-      <c r="AL8" t="inlineStr"/>
+        <v>-0.01714857057244679</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>6</v>
+      </c>
       <c r="AM8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
@@ -3196,83 +3225,87 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>36608</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>37538</v>
-      </c>
+        <v>35993</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>1896</v>
+        <v>90</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.4643360036641075</v>
+        <v>0</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.4686364820397299</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1894</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.3119812442777333</v>
+        <v>0</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.3119812442777333</v>
+        <v>0</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" t="b">
-        <v>1</v>
-      </c>
-      <c r="V9" s="3" t="n">
-        <v>-0.1533096362807653</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>638</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-31</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.4643360036641075</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.4686364820397299</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1258</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-55</v>
+      </c>
       <c r="AD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.8668419136628736</v>
+        <v>0</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.03316330717380855</v>
+        <v>-0.04500652696670188</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.04033580449562224</v>
-      </c>
-      <c r="AH9" t="inlineStr"/>
+        <v>0.1801116697737415</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-54</v>
+      </c>
       <c r="AI9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AN9" s="3" t="n">
+        <v>0.2791458357934953</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>-0.1971069850667453</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3321,89 +3354,99 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>37538</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>36105</v>
+      </c>
       <c r="M10" t="n">
-        <v>1896</v>
+        <v>79</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-0.4948749056728247</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-0.4989302081758815</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="P10" t="n">
-        <v>1894</v>
+        <v>78</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.2980003483950809</v>
+        <v>0.08993390447450868</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.2980003483950809</v>
+        <v>0.03892731995262652</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
       </c>
       <c r="U10" t="b">
-        <v>1</v>
-      </c>
-      <c r="V10" s="3" t="n">
-        <v>-0.08302907088810441</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>638</v>
+        <v>31</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.4948749056728247</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.4989302081758815</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1258</v>
-      </c>
-      <c r="AC10" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-7</v>
+      </c>
       <c r="AD10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.9797076233798998</v>
+        <v>0.1946904599376615</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>0.01918241129115617</v>
+        <v>-0.006079207014075362</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.009796902486905124</v>
-      </c>
-      <c r="AH10" t="inlineStr"/>
+        <v>0.01714857057244679</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-6</v>
+      </c>
       <c r="AI10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.1926401463891455</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.1981389748850485</v>
-      </c>
-      <c r="AL10" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
       <c r="AM10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AN10" s="3" t="n">
+        <v>0.2791458357934953</v>
+      </c>
+      <c r="AO10" s="3" t="n">
+        <v>-0.01828253075611685</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3700,68 +3743,66 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.4862309442441404</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.4862309442441404</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.2658275917027499</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.2658275917027499</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K2" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>41124</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1215</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.5035092528573142</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.5040024023286778</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1213</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.2354171526922748</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.1562892258388257</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>-0.03993583465459449</v>
+      </c>
       <c r="W2" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.5035092528573142</v>
+        <v>-0.4862309442441404</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441404</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>860</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>1.014136226616548</v>
+        <v>0.9463998245842093</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -3809,68 +3850,66 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.5038864433233317</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.5086484580604441</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1893</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.2788914529787295</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.2788914529787295</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K3" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>41117</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1210</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.5031043706109166</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.5082988629979938</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1207</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.2138272344349207</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.1416639151943617</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T3" t="b">
         <v>0</v>
       </c>
       <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>-0.02035410490055889</v>
+      </c>
       <c r="W3" t="n">
-        <v>355</v>
+        <v>637</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.5031043706109166</v>
+        <v>-0.5038864433233317</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.5082988629979938</v>
+        <v>-0.5086484580604441</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>855</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-5</v>
-      </c>
+        <v>1258</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>1.012495061044242</v>
+        <v>1.015667555425681</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -3878,11 +3917,9 @@
       <c r="AG3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ3" s="3" t="inlineStr"/>
       <c r="AK3" s="3" t="inlineStr"/>
@@ -3926,34 +3963,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>38028</v>
+      </c>
+      <c r="M4" t="n">
+        <v>974</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.2951492679396009</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.3383158398603918</v>
+      </c>
+      <c r="P4" t="n">
+        <v>769</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1469627184408073</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.1053877950228616</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>40956</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1099</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.4652359830536872</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.4652359830536872</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1098</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.2062376999383152</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.1302232557034226</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -3963,43 +4000,39 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.2951492679396009</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>744</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-116</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.8699837092823584</v>
+        <v>0.4187401027120015</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.01144065949093909</v>
+        <v>-0.1735036579558678</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.03786838755722943</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-111</v>
-      </c>
+        <v>0.2087371753837307</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ4" s="3" t="inlineStr"/>
       <c r="AK4" s="3" t="inlineStr"/>
@@ -4051,34 +4084,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>36893</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>39094</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1709</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.2072129787019408</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.2148226548093674</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1706</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.1623796973802989</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.1542093179696239</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>39412</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>41337</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1358</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.07677851489674281</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.08642977100026483</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1355</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.04081126075738026</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.02864269572822136</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -4088,43 +4121,39 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>33</v>
+        <v>195</v>
       </c>
       <c r="X5" t="n">
-        <v>-322</v>
+        <v>-442</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.07677851489674281</v>
+        <v>-0.2072129787019408</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.08642977100026483</v>
+        <v>-0.2148226548093674</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1325</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>465</v>
-      </c>
+        <v>1514</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.08316370029901932</v>
+        <v>0.261372819099212</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.1130212194661403</v>
+        <v>-0.1246821350091056</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.4263258557141738</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>470</v>
-      </c>
+        <v>0.2966734646213909</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ5" s="3" t="inlineStr"/>
       <c r="AK5" s="3" t="inlineStr"/>
@@ -4180,34 +4209,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>39211</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1789</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.44706498536634</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.4523724087433373</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1786</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.2366576472316186</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.2299470760608705</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>40955</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1098</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.4635884392739443</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.4691960268712783</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1095</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.2111591672112709</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.1332701653313692</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -4217,52 +4246,48 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.4635884392739443</v>
+        <v>-0.44706498536634</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.4691960268712783</v>
+        <v>-0.4523724087433373</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>743</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-117</v>
-      </c>
+        <v>1207</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.8642402088546672</v>
+        <v>0.8085307921086118</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.008393749862992517</v>
+        <v>-0.04894437691785897</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.03951593133697229</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>-112</v>
-      </c>
+        <v>0.05682145795699167</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.00304690962794657</v>
+        <v>0.1245592810380089</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>0.001647543779742855</v>
+        <v>-0.151915717426739</v>
       </c>
       <c r="AL6" t="n">
-        <v>-1</v>
+        <v>815</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
@@ -4313,80 +4338,76 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.5038864433233317</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.5086484580604441</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1893</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.2788914529787295</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.2788914529787295</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K7" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>40009</v>
-      </c>
-      <c r="M7" t="n">
-        <v>444</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.2683604314036379</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.2760089111735863</v>
-      </c>
-      <c r="P7" t="n">
-        <v>441</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.0780731145627515</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.03135491734221058</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T7" t="b">
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>-0.02035410490055889</v>
+      </c>
       <c r="W7" t="n">
-        <v>355</v>
+        <v>637</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.2683604314036379</v>
+        <v>-0.5038864433233317</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.2760089111735863</v>
+        <v>-0.5086484580604441</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>89</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-771</v>
-      </c>
+        <v>1258</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.3667932174834156</v>
+        <v>1.015667555425681</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.1103089978521511</v>
+        <v>0</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.2347439392072788</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-766</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
       <c r="AK7" s="3" t="inlineStr"/>
@@ -4442,92 +4463,86 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.5038864433233317</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.5086484580604441</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1893</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.2788914529787295</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.2788914529787295</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K8" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>40575</v>
-      </c>
-      <c r="M8" t="n">
-        <v>835</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.4717842240655957</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.4773061338280115</v>
-      </c>
-      <c r="P8" t="n">
-        <v>832</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.2107371766381855</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.1160027929701113</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T8" t="b">
         <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>-0.02035410490055889</v>
+      </c>
       <c r="W8" t="n">
-        <v>355</v>
+        <v>637</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.4717842240655957</v>
+        <v>-0.5038864433233317</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.4773061338280115</v>
+        <v>-0.5086484580604441</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>480</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-380</v>
-      </c>
+        <v>1258</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.8931657204501662</v>
+        <v>1.015667555425681</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.0256611222242504</v>
+        <v>0</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.03132014654532089</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>-375</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>-0.01422046273331132</v>
+        <v>0.1735036579558678</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.00654824101190854</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>-264</v>
-      </c>
+        <v>-0.2087371753837307</v>
+      </c>
+      <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
@@ -4575,80 +4590,76 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.4634866846191246</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.4686364820397297</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1893</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.3120635048494485</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.3120635048494485</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K9" s="2" t="n">
-        <v>40361</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>40486</v>
-      </c>
-      <c r="M9" t="n">
-        <v>775</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.1347647770726867</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.1549679774967497</v>
-      </c>
-      <c r="P9" t="n">
-        <v>754</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.05576233475633985</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.02957303924903827</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T9" t="b">
         <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>-0.1519671711234479</v>
+      </c>
       <c r="W9" t="n">
-        <v>688</v>
+        <v>637</v>
       </c>
       <c r="X9" t="n">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1347647770726867</v>
+        <v>-0.4634866846191246</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1549679774967497</v>
+        <v>-0.4686364820397297</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>87</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-773</v>
-      </c>
+        <v>1258</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.1557550750381416</v>
+        <v>0.8638866386570319</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.1120908759453234</v>
+        <v>0.03317205187071903</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.3683395935382299</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>-768</v>
-      </c>
+        <v>0.04039975870420709</v>
+      </c>
+      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
@@ -4704,92 +4715,86 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.4940740074126366</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.4989302081758814</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1893</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.2980789224083445</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.2980789224083445</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K10" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>41128</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1217</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.4635884392739443</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.4691960268712783</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1214</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.2078167550066812</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.138079228901551</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T10" t="b">
         <v>0</v>
       </c>
       <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V10" s="3" t="n">
+        <v>-0.08157517277451554</v>
+      </c>
       <c r="W10" t="n">
-        <v>355</v>
+        <v>637</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.4635884392739443</v>
+        <v>-0.4940740074126366</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.4691960268712783</v>
+        <v>-0.4989302081758814</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>862</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2</v>
-      </c>
+        <v>1258</v>
+      </c>
+      <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.8642402088546672</v>
+        <v>0.9765736780707504</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>-0.00358468629281064</v>
+        <v>0.01918746942961508</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.03951593133697229</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>7</v>
-      </c>
+        <v>0.009812435910695028</v>
+      </c>
+      <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.007855973198128446</v>
+        <v>0.1926911273854829</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>0.001647543779742855</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>118</v>
-      </c>
+        <v>-0.1989247394730357</v>
+      </c>
+      <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN10" s="3" t="inlineStr"/>
       <c r="AO10" s="3" t="inlineStr"/>
@@ -5089,34 +5094,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>43570</v>
+        <v>41124</v>
       </c>
       <c r="M2" t="n">
-        <v>140</v>
+        <v>1215</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>-0.195436869366569</v>
+        <v>-0.5035092528573142</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>-0.202297991486007</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="P2" t="n">
-        <v>132</v>
+        <v>1213</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.0826944425385638</v>
+        <v>0.2354171526922748</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.05218963375687856</v>
+        <v>0.1563175570682506</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -5126,22 +5131,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.195436869366569</v>
+        <v>-0.5035092528573142</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.202297991486007</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>76</v>
+        <v>860</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -5150,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.2429105460160745</v>
+        <v>1.014136226616548</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -5198,34 +5203,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>43537</v>
+        <v>41117</v>
       </c>
       <c r="M3" t="n">
-        <v>117</v>
+        <v>1210</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-0.1690941297033365</v>
+        <v>-0.5031043706109166</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.5082988629979938</v>
       </c>
       <c r="P3" t="n">
-        <v>107</v>
+        <v>1207</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.06490513107985459</v>
+        <v>0.2138272344349207</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.037472994900742</v>
+        <v>0.1416895952299563</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -5235,31 +5240,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.1690941297033365</v>
+        <v>-0.5031043706109166</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.5082988629979938</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>53</v>
+        <v>855</v>
       </c>
       <c r="AC3" t="n">
-        <v>-23</v>
+        <v>-5</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.2035057588929583</v>
+        <v>1.012495061044242</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -5315,34 +5320,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>43559</v>
+        <v>40956</v>
       </c>
       <c r="M4" t="n">
-        <v>133</v>
+        <v>1099</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="P4" t="n">
-        <v>131</v>
+        <v>1098</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.04836031164019643</v>
+        <v>0.2062376999383152</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.02975362321475319</v>
+        <v>0.1302468618407874</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -5352,40 +5357,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>69</v>
+        <v>744</v>
       </c>
       <c r="AC4" t="n">
-        <v>-7</v>
+        <v>-116</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.1715670148335215</v>
+        <v>0.8699837092823584</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.00771937168598881</v>
+        <v>-0.01144273338916893</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.0226517899470392</v>
+        <v>0.03786838755722943</v>
       </c>
       <c r="AH4" t="n">
-        <v>16</v>
+        <v>-111</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -5440,34 +5445,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>43458</v>
+        <v>39412</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>43537</v>
+        <v>41337</v>
       </c>
       <c r="M5" t="n">
-        <v>117</v>
+        <v>1358</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.1690941297033368</v>
+        <v>-0.07677851489674281</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.1775169494986037</v>
+        <v>-0.08642977100026483</v>
       </c>
       <c r="P5" t="n">
-        <v>107</v>
+        <v>1355</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.0649051310798547</v>
+        <v>0.04081126075738026</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.03747299490074205</v>
+        <v>0.02864788791456478</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -5477,40 +5482,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-322</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.1690941297033368</v>
+        <v>-0.07677851489674281</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1775169494986037</v>
+        <v>-0.08642977100026483</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>53</v>
+        <v>1325</v>
       </c>
       <c r="AC5" t="n">
-        <v>-23</v>
+        <v>465</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.2035057588929587</v>
+        <v>0.08316370029901932</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>-0.1130417073153916</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>-3.33066907387547e-16</v>
+        <v>0.4263258557141738</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -5569,34 +5574,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>43537</v>
+        <v>40955</v>
       </c>
       <c r="M6" t="n">
-        <v>117</v>
+        <v>1098</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.1690941297033365</v>
+        <v>-0.4635884392739443</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.4691960268712783</v>
       </c>
       <c r="P6" t="n">
-        <v>107</v>
+        <v>1095</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.06490513107985459</v>
+        <v>0.2111591672112709</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.037472994900742</v>
+        <v>0.1332943237953275</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -5606,52 +5611,52 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.1690941297033365</v>
+        <v>-0.4635884392739443</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.4691960268712783</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>53</v>
+        <v>743</v>
       </c>
       <c r="AC6" t="n">
-        <v>-23</v>
+        <v>-117</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.2035057588929583</v>
+        <v>0.8642402088546672</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0</v>
+        <v>-0.00839527143462887</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0</v>
+        <v>0.03951593133697229</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>-112</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.00771937168598881</v>
+        <v>0.003047461954540059</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.0226517899470392</v>
+        <v>0.001647543779742855</v>
       </c>
       <c r="AL6" t="n">
-        <v>-16</v>
+        <v>-1</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
@@ -5702,76 +5707,80 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>43458</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+        <v>39881</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>40009</v>
+      </c>
       <c r="M7" t="n">
-        <v>353</v>
+        <v>444</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.1690941297033365</v>
+        <v>-0.2683604314036379</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.2760089111735863</v>
       </c>
       <c r="P7" t="n">
-        <v>344</v>
+        <v>441</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.09498192857031149</v>
+        <v>0.0780731145627515</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.09498192857031149</v>
+        <v>0.03136060118479189</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>1</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>-0.034183156802571</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.1690941297033365</v>
+        <v>-0.2683604314036379</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.2760089111735863</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>289</v>
-      </c>
-      <c r="AC7" t="inlineStr"/>
+        <v>89</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-771</v>
+      </c>
       <c r="AD7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.2035057588929583</v>
+        <v>0.3667932174834156</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.05750893366956949</v>
+        <v>-0.1103289940451644</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr"/>
+        <v>0.2347439392072788</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-766</v>
+      </c>
       <c r="AI7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
       <c r="AK7" s="3" t="inlineStr"/>
@@ -5827,34 +5836,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>43630</v>
+        <v>40575</v>
       </c>
       <c r="M8" t="n">
-        <v>182</v>
+        <v>835</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.1690941297033365</v>
+        <v>-0.4717842240655957</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.4773061338280115</v>
       </c>
       <c r="P8" t="n">
-        <v>172</v>
+        <v>832</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.06074643438348071</v>
+        <v>0.2107371766381855</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.04367618583846061</v>
+        <v>0.1160238213021919</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -5864,52 +5873,52 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1690941297033365</v>
+        <v>-0.4717842240655957</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.4773061338280115</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>118</v>
+        <v>480</v>
       </c>
       <c r="AC8" t="n">
-        <v>42</v>
+        <v>-380</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.2035057588929583</v>
+        <v>0.8931657204501662</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.006203190937718608</v>
+        <v>-0.02566577392776441</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0</v>
+        <v>0.03132014654532089</v>
       </c>
       <c r="AH8" t="n">
-        <v>65</v>
+        <v>-375</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.01392256262370742</v>
+        <v>-0.01422304053859548</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.0226517899470392</v>
+        <v>-0.00654824101190854</v>
       </c>
       <c r="AL8" t="n">
-        <v>49</v>
+        <v>-264</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
@@ -5960,76 +5969,80 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>43458</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
+        <v>40361</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>40486</v>
+      </c>
       <c r="M9" t="n">
-        <v>353</v>
+        <v>775</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.1690941297033368</v>
+        <v>-0.1347647770726867</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.1775169494986037</v>
+        <v>-0.1549679774967497</v>
       </c>
       <c r="P9" t="n">
-        <v>344</v>
+        <v>754</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.09498192857031149</v>
+        <v>0.05576233475633985</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.09498192857031149</v>
+        <v>0.02957840008280822</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>1</v>
-      </c>
-      <c r="V9" s="3" t="n">
-        <v>-0.03418315680257089</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>64</v>
+        <v>688</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1690941297033368</v>
+        <v>-0.1347647770726867</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1775169494986037</v>
+        <v>-0.1549679774967497</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>289</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>87</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-773</v>
+      </c>
       <c r="AD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.2035057588929587</v>
+        <v>0.1557550750381416</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.05750893366956949</v>
+        <v>-0.1121111951471481</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>-3.33066907387547e-16</v>
-      </c>
-      <c r="AH9" t="inlineStr"/>
+        <v>0.3683395935382299</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-768</v>
+      </c>
       <c r="AI9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
@@ -6085,34 +6098,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>43630</v>
+        <v>41128</v>
       </c>
       <c r="M10" t="n">
-        <v>182</v>
+        <v>1217</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-0.1690941297033365</v>
+        <v>-0.4635884392739443</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.4691960268712783</v>
       </c>
       <c r="P10" t="n">
-        <v>172</v>
+        <v>1214</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.06074643438348071</v>
+        <v>0.2078167550066812</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.04367618583846061</v>
+        <v>0.1381042591254313</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -6122,52 +6135,52 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.1690941297033365</v>
+        <v>-0.4635884392739443</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.4691960268712783</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
+        <v>862</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="3" t="n">
+        <v>0.8642402088546672</v>
+      </c>
+      <c r="AF10" s="3" t="n">
+        <v>-0.003585336104524994</v>
+      </c>
+      <c r="AG10" s="3" t="n">
+        <v>0.03951593133697229</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="3" t="n">
+        <v>0.007857397284643935</v>
+      </c>
+      <c r="AK10" s="3" t="n">
+        <v>0.001647543779742855</v>
+      </c>
+      <c r="AL10" t="n">
         <v>118</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.2035057588929583</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>0.006203190937718608</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>65</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.01392256262370742</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>-0.0226517899470392</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>49</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
@@ -6470,34 +6483,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>43572</v>
+      </c>
+      <c r="M2" t="n">
+        <v>143</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.1989728318606707</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.202297991486007</v>
+      </c>
+      <c r="P2" t="n">
+        <v>138</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.08183226369428304</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.0521184671904906</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>43992</v>
-      </c>
-      <c r="M2" t="n">
-        <v>78</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.2902196151348784</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.2902196151348784</v>
-      </c>
-      <c r="P2" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1403286526425156</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.05728893254440424</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -6507,22 +6520,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.1989728318606707</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.202297991486007</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -6531,7 +6544,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.4088864968986545</v>
+        <v>0.2483971078320051</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -6579,34 +6592,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>43537</v>
+      </c>
+      <c r="M3" t="n">
+        <v>118</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.1712229343499421</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.1775169494986033</v>
+      </c>
+      <c r="P3" t="n">
+        <v>111</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.06463413170556485</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.03742150269784624</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>44032</v>
-      </c>
-      <c r="M3" t="n">
-        <v>105</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.3111804093256711</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.3111804093256711</v>
-      </c>
-      <c r="P3" t="n">
-        <v>104</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.1334744213775015</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.06311924691882544</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -6616,31 +6629,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1712229343499421</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1775169494986033</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="AC3" t="n">
-        <v>27</v>
+        <v>-25</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.4517589417296293</v>
+        <v>0.2065970952220328</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -6696,34 +6709,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>43559</v>
+      </c>
+      <c r="M4" t="n">
+        <v>134</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.1461536977865012</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.1465009124724216</v>
+      </c>
+      <c r="P4" t="n">
+        <v>130</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.04818086645128587</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.02971168714991625</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>44055</v>
-      </c>
-      <c r="M4" t="n">
-        <v>122</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="P4" t="n">
-        <v>121</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1177175505348945</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.05996593388725459</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -6733,40 +6746,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1461536977865012</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="AC4" t="n">
-        <v>44</v>
+        <v>-9</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.4089398190385185</v>
+        <v>0.1711709676643378</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.003153313031570848</v>
+        <v>-0.007709815547929991</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.02093393214285921</v>
+        <v>0.02506923656344084</v>
       </c>
       <c r="AH4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -6821,34 +6834,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>43537</v>
+      </c>
+      <c r="M5" t="n">
+        <v>118</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.1712229343499425</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.1775169494986037</v>
+      </c>
+      <c r="P5" t="n">
+        <v>111</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.06463413170556499</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.03742150269784631</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>44032</v>
-      </c>
-      <c r="M5" t="n">
-        <v>105</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.3111804093256713</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.3111804093256713</v>
-      </c>
-      <c r="P5" t="n">
-        <v>104</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.1334744213775015</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.06311924691882546</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -6858,37 +6871,37 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.3111804093256713</v>
+        <v>-0.1712229343499425</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.3111804093256713</v>
+        <v>-0.1775169494986037</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="AC5" t="n">
-        <v>27</v>
+        <v>-25</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.4517589417296295</v>
+        <v>0.2065970952220335</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>6.938893903907228e-17</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>-4.440892098500626e-16</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -6950,34 +6963,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>43537</v>
+      </c>
+      <c r="M6" t="n">
+        <v>118</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.1712229343499421</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.1775169494986033</v>
+      </c>
+      <c r="P6" t="n">
+        <v>111</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.06463413170556485</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.03742150269784624</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>44032</v>
-      </c>
-      <c r="M6" t="n">
-        <v>105</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.3111804093256711</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.3111804093256711</v>
-      </c>
-      <c r="P6" t="n">
-        <v>104</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.1334744213775015</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.06311924691882544</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -6987,31 +7000,31 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1712229343499421</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1775169494986033</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="AC6" t="n">
-        <v>27</v>
+        <v>-25</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.4517589417296293</v>
+        <v>0.2065970952220328</v>
       </c>
       <c r="AF6" s="3" t="n">
         <v>0</v>
@@ -7026,13 +7039,13 @@
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.003153313031570848</v>
+        <v>0.007709815547929991</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.02093393214285921</v>
+        <v>-0.02506923656344084</v>
       </c>
       <c r="AL6" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
@@ -7083,80 +7096,76 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>354</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.1712229343499421</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.1775169494986033</v>
+      </c>
+      <c r="P7" t="n">
+        <v>348</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.09484857918033605</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.09484857918033605</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="K7" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>44032</v>
-      </c>
-      <c r="M7" t="n">
-        <v>105</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.3111804093256711</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.3111804093256711</v>
-      </c>
-      <c r="P7" t="n">
-        <v>104</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.1334744213775015</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.06311924691882544</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>44564</v>
-      </c>
       <c r="T7" t="b">
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>-0.03665760722718359</v>
+      </c>
       <c r="W7" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1712229343499421</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1775169494986033</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>82</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>27</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.4517589417296293</v>
+        <v>0.2065970952220328</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0</v>
+        <v>0.05742707648248981</v>
       </c>
       <c r="AG7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
       <c r="AK7" s="3" t="inlineStr"/>
@@ -7212,34 +7221,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>43634</v>
+      </c>
+      <c r="M8" t="n">
+        <v>185</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.1712229343499421</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.1775169494986033</v>
+      </c>
+      <c r="P8" t="n">
+        <v>178</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.06026199405008715</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.04362001331609051</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>44032</v>
-      </c>
-      <c r="M8" t="n">
-        <v>105</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.3111804093256711</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.3111804093256711</v>
-      </c>
-      <c r="P8" t="n">
-        <v>104</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.1334744213775015</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.06311924691882544</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -7249,52 +7258,52 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1712229343499421</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1775169494986033</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AC8" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.4517589417296293</v>
+        <v>0.2065970952220328</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0</v>
+        <v>0.006198510618244273</v>
       </c>
       <c r="AG8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.003153313031570848</v>
+        <v>0.01390832616617426</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.02093393214285921</v>
+        <v>-0.02506923656344084</v>
       </c>
       <c r="AL8" t="n">
-        <v>-17</v>
+        <v>51</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
@@ -7345,80 +7354,76 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>354</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.1712229343499424</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.1775169494986036</v>
+      </c>
+      <c r="P9" t="n">
+        <v>348</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.09484857918033605</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.09484857918033605</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="K9" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>44032</v>
-      </c>
-      <c r="M9" t="n">
-        <v>105</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.3111804093256714</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.3111804093256714</v>
-      </c>
-      <c r="P9" t="n">
-        <v>104</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.1334744213775014</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.06311924691882538</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>44564</v>
-      </c>
       <c r="T9" t="b">
         <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>-0.03665760722718348</v>
+      </c>
       <c r="W9" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.3111804093256714</v>
+        <v>-0.1712229343499424</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.3111804093256714</v>
+        <v>-0.1775169494986036</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>82</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>27</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.4517589417296297</v>
+        <v>0.2065970952220335</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-5.551115123125783e-17</v>
+        <v>0.05742707648248981</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>-2.220446049250313e-16</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
+        <v>-3.33066907387547e-16</v>
+      </c>
+      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
@@ -7474,34 +7479,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>43634</v>
+      </c>
+      <c r="M10" t="n">
+        <v>185</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.1712229343499421</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.1775169494986033</v>
+      </c>
+      <c r="P10" t="n">
+        <v>178</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.06026199405008715</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.04362001331609051</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>44032</v>
-      </c>
-      <c r="M10" t="n">
-        <v>105</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.3111804093256711</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.3111804093256711</v>
-      </c>
-      <c r="P10" t="n">
-        <v>104</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1334744213775015</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.06311924691882544</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -7511,52 +7516,52 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1712229343499421</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1775169494986033</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AC10" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.4517589417296293</v>
+        <v>0.2065970952220328</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>0</v>
+        <v>0.006198510618244273</v>
       </c>
       <c r="AG10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.003153313031570848</v>
+        <v>0.01390832616617426</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.02093393214285921</v>
+        <v>-0.02506923656344084</v>
       </c>
       <c r="AL10" t="n">
-        <v>-17</v>
+        <v>51</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
@@ -7859,34 +7864,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>43992</v>
+      </c>
+      <c r="M2" t="n">
+        <v>78</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.2902196151348784</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2902196151348784</v>
+      </c>
+      <c r="P2" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1403286526425156</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.05728893254440424</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>44931</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>45250</v>
-      </c>
-      <c r="M2" t="n">
-        <v>473</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.3239608533428747</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.3239608533428747</v>
-      </c>
-      <c r="P2" t="n">
-        <v>472</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1873955345996989</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.1456175032694574</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -7896,22 +7901,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>253</v>
+        <v>23</v>
       </c>
       <c r="X2" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.3239608533428747</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.3239608533428747</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -7920,7 +7925,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.4792042812088539</v>
+        <v>0.4088864968986545</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -7968,34 +7973,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>44032</v>
+      </c>
+      <c r="M3" t="n">
+        <v>105</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.3111804093256711</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.3111804093256711</v>
+      </c>
+      <c r="P3" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.1334744213775015</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.06311924691882544</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>45054</v>
-      </c>
-      <c r="M3" t="n">
-        <v>337</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.2944579323458331</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.2944579323458331</v>
-      </c>
-      <c r="P3" t="n">
-        <v>336</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.1702187018471014</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.1116942447466524</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -8005,31 +8010,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AC3" t="n">
-        <v>-78</v>
+        <v>27</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.4173499297141365</v>
+        <v>0.4517589417296293</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -8085,34 +8090,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>44055</v>
+      </c>
+      <c r="M4" t="n">
+        <v>122</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="P4" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1177175505348945</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.05996593388725459</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>45121</v>
-      </c>
-      <c r="M4" t="n">
-        <v>383</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.2382824194485816</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.2382824194485816</v>
-      </c>
-      <c r="P4" t="n">
-        <v>382</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1328475678049171</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.09291469197671884</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -8122,40 +8127,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>188</v>
+        <v>99</v>
       </c>
       <c r="AC4" t="n">
-        <v>-32</v>
+        <v>44</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.3128225283655466</v>
+        <v>0.4089398190385185</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.01877955276993357</v>
+        <v>-0.003153313031570848</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.05617551289725142</v>
+        <v>0.02093393214285921</v>
       </c>
       <c r="AH4" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -8210,73 +8215,77 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>44032</v>
+      </c>
+      <c r="M5" t="n">
+        <v>105</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.3111804093256713</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.3111804093256713</v>
+      </c>
+      <c r="P5" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.1334744213775015</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.06311924691882546</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" t="n">
-        <v>513</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.0108368102681341</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.0007180668185548988</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>45707</v>
-      </c>
       <c r="T5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="X5" t="n">
-        <v>-195</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0</v>
+        <v>-0.3111804093256713</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0</v>
+        <v>-0.3111804093256713</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AC5" t="n">
-        <v>-220</v>
+        <v>27</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0</v>
+        <v>0.4517589417296295</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.1116942447466524</v>
+        <v>2.775557561562891e-17</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.2944579323458331</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="AH5" t="n">
-        <v>-142</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -8285,12 +8294,8 @@
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="n">
-        <v>0.3763450826954717</v>
-      </c>
-      <c r="AO5" s="3" t="n">
-        <v>-0.2731079632649366</v>
-      </c>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8339,34 +8344,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>44032</v>
+      </c>
+      <c r="M6" t="n">
+        <v>105</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.3111804093256711</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.3111804093256711</v>
+      </c>
+      <c r="P6" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.1334744213775015</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.06311924691882544</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>45121</v>
-      </c>
-      <c r="M6" t="n">
-        <v>383</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.2382824194485826</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.2382824194485826</v>
-      </c>
-      <c r="P6" t="n">
-        <v>382</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.1328475678049178</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.09291469197671932</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -8376,62 +8381,58 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="AC6" t="n">
-        <v>-32</v>
+        <v>27</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.3128225283655484</v>
+        <v>0.4517589417296293</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.01877955276993308</v>
+        <v>0</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.05617551289725042</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>4.85722573273506e-16</v>
+        <v>0.003153313031570848</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-9.992007221626409e-16</v>
+        <v>-0.02093393214285921</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
       </c>
-      <c r="AN6" s="3" t="n">
-        <v>0.3763450826954717</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>-0.1002927315345143</v>
-      </c>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8476,34 +8477,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>44032</v>
+      </c>
+      <c r="M7" t="n">
+        <v>105</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.3111804093256711</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.3111804093256711</v>
+      </c>
+      <c r="P7" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.1334744213775015</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.06311924691882544</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>45440</v>
-      </c>
-      <c r="M7" t="n">
-        <v>602</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.2944579323458331</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.2944579323458331</v>
-      </c>
-      <c r="P7" t="n">
-        <v>601</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.1877948800880885</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.1645915652982076</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -8513,40 +8514,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>407</v>
+        <v>82</v>
       </c>
       <c r="AC7" t="n">
-        <v>187</v>
+        <v>27</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.4173499297141365</v>
+        <v>0.4517589417296293</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.05289732055155524</v>
+        <v>0</v>
       </c>
       <c r="AG7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -8605,34 +8606,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>44032</v>
+      </c>
+      <c r="M8" t="n">
+        <v>105</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.3111804093256711</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.3111804093256711</v>
+      </c>
+      <c r="P8" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.1334744213775015</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.06311924691882544</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>45301</v>
-      </c>
-      <c r="M8" t="n">
-        <v>507</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.2944579323458331</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.2944579323458331</v>
-      </c>
-      <c r="P8" t="n">
-        <v>506</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.1635678614010515</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.1315815515882588</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -8642,52 +8643,52 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>312</v>
+        <v>82</v>
       </c>
       <c r="AC8" t="n">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.4173499297141365</v>
+        <v>0.4517589417296293</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.01988730684160644</v>
+        <v>0</v>
       </c>
       <c r="AG8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.03866685961154001</v>
+        <v>0.003153313031570848</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.05617551289725142</v>
+        <v>-0.02093393214285921</v>
       </c>
       <c r="AL8" t="n">
-        <v>124</v>
+        <v>-17</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
@@ -8738,73 +8739,77 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>44032</v>
+      </c>
+      <c r="M9" t="n">
+        <v>105</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.3111804093256714</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.3111804093256714</v>
+      </c>
+      <c r="P9" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.1334744213775014</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.06311924691882538</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" t="n">
-        <v>513</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.0108368102681341</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.000718066818554894</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>45707</v>
-      </c>
       <c r="T9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="X9" t="n">
-        <v>-195</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>0</v>
+        <v>-0.3111804093256714</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>0</v>
+        <v>-0.3111804093256714</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AC9" t="n">
-        <v>-220</v>
+        <v>27</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0</v>
+        <v>0.4517589417296297</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.1116942447466524</v>
+        <v>-5.551115123125783e-17</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.2944579323458331</v>
+        <v>-2.220446049250313e-16</v>
       </c>
       <c r="AH9" t="n">
-        <v>-142</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -8863,34 +8868,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>44032</v>
+      </c>
+      <c r="M10" t="n">
+        <v>105</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.3111804093256711</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.3111804093256711</v>
+      </c>
+      <c r="P10" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.1334744213775015</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.06311924691882544</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>45121</v>
-      </c>
-      <c r="M10" t="n">
-        <v>383</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.2382824194485826</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.2382824194485826</v>
-      </c>
-      <c r="P10" t="n">
-        <v>382</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1328475678049178</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.09291469197671932</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -8900,52 +8905,52 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="AC10" t="n">
-        <v>-32</v>
+        <v>27</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.3128225283655484</v>
+        <v>0.4517589417296293</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>-0.01877955276993308</v>
+        <v>0</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.05617551289725042</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>4.85722573273506e-16</v>
+        <v>0.003153313031570848</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-9.992007221626409e-16</v>
+        <v>-0.02093393214285921</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
@@ -9248,34 +9253,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>44931</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="M2" t="n">
+        <v>473</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.3239608533428747</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.3239608533428747</v>
+      </c>
+      <c r="P2" t="n">
+        <v>472</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1873955345996989</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.1456175032694574</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>45835</v>
-      </c>
-      <c r="M2" t="n">
-        <v>89</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.2242012270138071</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.2242012270138071</v>
-      </c>
-      <c r="P2" t="n">
-        <v>88</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1032426212645815</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.06633642004451827</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -9285,22 +9290,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428747</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428747</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>55</v>
+        <v>220</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -9309,7 +9314,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.2889940469367012</v>
+        <v>0.4792042812088539</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -9357,34 +9362,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45054</v>
+      </c>
+      <c r="M3" t="n">
+        <v>337</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.2944579323458331</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.2944579323458331</v>
+      </c>
+      <c r="P3" t="n">
+        <v>336</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.1702187018471014</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.1116942447466524</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>45855</v>
-      </c>
-      <c r="M3" t="n">
-        <v>102</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.2044491165694975</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.2044491165694975</v>
-      </c>
-      <c r="P3" t="n">
-        <v>101</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.09752257841525133</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.06703406261266386</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -9394,31 +9399,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.2044491165694975</v>
+        <v>-0.2944579323458331</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.2044491165694975</v>
+        <v>-0.2944579323458331</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>68</v>
+        <v>142</v>
       </c>
       <c r="AC3" t="n">
-        <v>13</v>
+        <v>-78</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.2569906222564804</v>
+        <v>0.4173499297141365</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -9474,34 +9479,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>45121</v>
+      </c>
+      <c r="M4" t="n">
+        <v>383</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.2382824194485816</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.2382824194485816</v>
+      </c>
+      <c r="P4" t="n">
+        <v>382</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1328475678049171</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.09291469197671884</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>45863</v>
-      </c>
-      <c r="M4" t="n">
-        <v>108</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.1556116196127491</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.1556116196127491</v>
-      </c>
-      <c r="P4" t="n">
-        <v>107</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.06372707386676911</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.04506184607636846</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -9511,40 +9516,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="AC4" t="n">
-        <v>19</v>
+        <v>-32</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.184289153222813</v>
+        <v>0.3128225283655466</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.0219722165362954</v>
+        <v>-0.01877955276993357</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.04883749695674844</v>
+        <v>0.05617551289725142</v>
       </c>
       <c r="AH4" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -9599,30 +9604,30 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>45707</v>
+        <v>44564</v>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>88</v>
+        <v>513</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>0</v>
+        <v>-0.0108368102681341</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0</v>
+        <v>0.0007180668185548988</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>46021</v>
+        <v>45707</v>
       </c>
       <c r="T5" t="b">
         <v>1</v>
@@ -9635,7 +9640,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-34</v>
+        <v>-195</v>
       </c>
       <c r="Y5" s="3" t="n">
         <v>0</v>
@@ -9650,7 +9655,7 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>-55</v>
+        <v>-220</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
@@ -9659,13 +9664,13 @@
         <v>0</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.06703406261266386</v>
+        <v>-0.1116942447466524</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.2044491165694975</v>
+        <v>0.2944579323458331</v>
       </c>
       <c r="AH5" t="n">
-        <v>-68</v>
+        <v>-142</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -9675,10 +9680,10 @@
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" s="3" t="n">
-        <v>0.02318587671251238</v>
+        <v>0.3763450826954717</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.01772738840404031</v>
+        <v>-0.2731079632649366</v>
       </c>
     </row>
     <row r="6">
@@ -9728,34 +9733,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>45121</v>
+      </c>
+      <c r="M6" t="n">
+        <v>383</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.2382824194485826</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.2382824194485826</v>
+      </c>
+      <c r="P6" t="n">
+        <v>382</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.1328475678049178</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.09291469197671932</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>45863</v>
-      </c>
-      <c r="M6" t="n">
-        <v>108</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.1556116196127489</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.1556116196127489</v>
-      </c>
-      <c r="P6" t="n">
-        <v>107</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.06372707386676901</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.04506184607636839</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -9765,49 +9770,49 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="AC6" t="n">
-        <v>19</v>
+        <v>-32</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.1842891532228128</v>
+        <v>0.3128225283655484</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.02197221653629547</v>
+        <v>-0.01877955276993308</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.04883749695674855</v>
+        <v>0.05617551289725042</v>
       </c>
       <c r="AH6" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>-6.938893903907228e-17</v>
+        <v>4.85722573273506e-16</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>-9.992007221626409e-16</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -9816,10 +9821,10 @@
         <v>0</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.02318587671251238</v>
+        <v>0.3763450826954717</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>0.04172379361860035</v>
+        <v>-0.1002927315345143</v>
       </c>
     </row>
     <row r="7">
@@ -9865,73 +9870,77 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>45440</v>
+      </c>
+      <c r="M7" t="n">
+        <v>602</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.2944579323458331</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.2944579323458331</v>
+      </c>
+      <c r="P7" t="n">
+        <v>601</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.1877948800880885</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.1645915652982076</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" t="n">
-        <v>88</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>46021</v>
-      </c>
       <c r="T7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="X7" t="n">
-        <v>-34</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0</v>
+        <v>-0.2944579323458331</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0</v>
+        <v>-0.2944579323458331</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>407</v>
       </c>
       <c r="AC7" t="n">
-        <v>-55</v>
+        <v>187</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0</v>
+        <v>0.4173499297141365</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.06703406261266386</v>
+        <v>0.05289732055155524</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.2044491165694975</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-68</v>
+        <v>265</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -9940,12 +9949,8 @@
       <c r="AK7" s="3" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
-      <c r="AN7" s="3" t="n">
-        <v>0.02318587671251238</v>
-      </c>
-      <c r="AO7" s="3" t="n">
-        <v>-0.01772738840404031</v>
-      </c>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9994,34 +9999,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>45301</v>
+      </c>
+      <c r="M8" t="n">
+        <v>507</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.2944579323458331</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.2944579323458331</v>
+      </c>
+      <c r="P8" t="n">
+        <v>506</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.1635678614010515</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.1315815515882588</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>45863</v>
-      </c>
-      <c r="M8" t="n">
-        <v>108</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.1556116196127489</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.1556116196127489</v>
-      </c>
-      <c r="P8" t="n">
-        <v>107</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.06372707386676901</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.04506184607636839</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -10031,62 +10036,58 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2944579323458331</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2944579323458331</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>74</v>
+        <v>312</v>
       </c>
       <c r="AC8" t="n">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.1842891532228128</v>
+        <v>0.4173499297141365</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.02197221653629547</v>
+        <v>0.01988730684160644</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.04883749695674855</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>-6.938893903907228e-17</v>
+        <v>0.03866685961154001</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>-0.05617551289725142</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
       </c>
-      <c r="AN8" s="3" t="n">
-        <v>0.02318587671251238</v>
-      </c>
-      <c r="AO8" s="3" t="n">
-        <v>0.04172379361860035</v>
-      </c>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10131,30 +10132,30 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>45707</v>
+        <v>44564</v>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>88</v>
+        <v>513</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0</v>
+        <v>-0.0108368102681341</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0</v>
+        <v>0.000718066818554894</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>46021</v>
+        <v>45707</v>
       </c>
       <c r="T9" t="b">
         <v>1</v>
@@ -10167,7 +10168,7 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-34</v>
+        <v>-195</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>0</v>
@@ -10182,7 +10183,7 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>-55</v>
+        <v>-220</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
@@ -10191,13 +10192,13 @@
         <v>0</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.06703406261266386</v>
+        <v>-0.1116942447466524</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.2044491165694975</v>
+        <v>0.2944579323458331</v>
       </c>
       <c r="AH9" t="n">
-        <v>-68</v>
+        <v>-142</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -10206,12 +10207,8 @@
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="n">
-        <v>0.02318587671251238</v>
-      </c>
-      <c r="AO9" s="3" t="n">
-        <v>-0.01772738840404031</v>
-      </c>
+      <c r="AN9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10260,34 +10257,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>45121</v>
+      </c>
+      <c r="M10" t="n">
+        <v>383</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.2382824194485826</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.2382824194485826</v>
+      </c>
+      <c r="P10" t="n">
+        <v>382</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.1328475678049178</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.09291469197671932</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>45863</v>
-      </c>
-      <c r="M10" t="n">
-        <v>108</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.1556116196127489</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.1556116196127489</v>
-      </c>
-      <c r="P10" t="n">
-        <v>107</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.06372707386676901</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.04506184607636839</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -10297,49 +10294,49 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="AC10" t="n">
-        <v>19</v>
+        <v>-32</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.1842891532228128</v>
+        <v>0.3128225283655484</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>-0.02197221653629547</v>
+        <v>-0.01877955276993308</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.04883749695674855</v>
+        <v>0.05617551289725042</v>
       </c>
       <c r="AH10" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>-6.938893903907228e-17</v>
+        <v>4.85722573273506e-16</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>-9.992007221626409e-16</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -10347,12 +10344,8 @@
       <c r="AM10" t="b">
         <v>0</v>
       </c>
-      <c r="AN10" s="3" t="n">
-        <v>0.02318587671251238</v>
-      </c>
-      <c r="AO10" s="3" t="n">
-        <v>0.04172379361860035</v>
-      </c>
+      <c r="AN10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10365,7 +10358,1408 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AO10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="19" customWidth="1" min="29" max="29"/>
+    <col width="23" customWidth="1" min="30" max="30"/>
+    <col width="20" customWidth="1" min="31" max="31"/>
+    <col width="19" customWidth="1" min="32" max="32"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="17" customWidth="1" min="34" max="34"/>
+    <col width="21" customWidth="1" min="35" max="35"/>
+    <col width="17" customWidth="1" min="36" max="36"/>
+    <col width="16" customWidth="1" min="37" max="37"/>
+    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="14" customWidth="1" min="40" max="40"/>
+    <col width="17" customWidth="1" min="41" max="41"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>base_run</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>peak_date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>trough_date</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>recovery_date</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_days</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_anchored_dd</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_hwm_dd</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_days_underwater</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>full_no_drawdown</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>full_not_recovered</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days_vs_defined</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_depth</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_trough_at_boundary</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days_vs_bench</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_vs_bench_censored</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_return_to_even</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_base_ulcer</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_base_depth</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base_days</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base_censored</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_fb_ulcer</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_fb_depth</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb_days</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb_censored</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>missed_rally</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pre_peak_d_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45835</v>
+      </c>
+      <c r="M2" t="n">
+        <v>89</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="P2" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1032426212645815</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.06633642004451827</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>34</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="AA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="3" t="n">
+        <v>0.2889940469367012</v>
+      </c>
+      <c r="AF2" s="3" t="inlineStr"/>
+      <c r="AG2" s="3" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" s="3" t="inlineStr"/>
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45855</v>
+      </c>
+      <c r="M3" t="n">
+        <v>102</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.2044491165694975</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.2044491165694975</v>
+      </c>
+      <c r="P3" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.09752257841525133</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.06703406261266386</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" s="3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>34</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>-0.2044491165694975</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>-0.2044491165694975</v>
+      </c>
+      <c r="AA3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>68</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>0.2569906222564804</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="M4" t="n">
+        <v>108</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.1556116196127491</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.1556116196127491</v>
+      </c>
+      <c r="P4" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.06372707386676911</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.04506184607636846</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>34</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>-0.1556116196127491</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>-0.1556116196127491</v>
+      </c>
+      <c r="AA4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>74</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>0.184289153222813</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>-0.0219722165362954</v>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>0.04883749695674844</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>89</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T5" t="b">
+        <v>1</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="3" t="n">
+        <v>-0.06703406261266386</v>
+      </c>
+      <c r="AG5" s="3" t="n">
+        <v>0.2044491165694975</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-68</v>
+      </c>
+      <c r="AI5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" s="3" t="n">
+        <v>0.02318587671251238</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>-0.01772738840404031</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_changepoint_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="M6" t="n">
+        <v>108</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="P6" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.06372707386676901</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.04506184607636839</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>34</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="AA6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>74</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="3" t="n">
+        <v>0.1842891532228128</v>
+      </c>
+      <c r="AF6" s="3" t="n">
+        <v>-0.02197221653629547</v>
+      </c>
+      <c r="AG6" s="3" t="n">
+        <v>0.04883749695674855</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="3" t="n">
+        <v>-6.938893903907228e-17</v>
+      </c>
+      <c r="AK6" s="3" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="3" t="n">
+        <v>0.02318587671251238</v>
+      </c>
+      <c r="AO6" s="3" t="n">
+        <v>0.04172379361860035</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>89</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T7" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="3" t="n">
+        <v>-0.06703406261266386</v>
+      </c>
+      <c r="AG7" s="3" t="n">
+        <v>0.2044491165694975</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-68</v>
+      </c>
+      <c r="AI7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" s="3" t="n">
+        <v>0.02318587671251238</v>
+      </c>
+      <c r="AO7" s="3" t="n">
+        <v>-0.01772738840404031</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_hmm_gspc_hrp</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="M8" t="n">
+        <v>108</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="P8" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.06372707386676901</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.04506184607636839</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>34</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="AA8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>74</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3" t="n">
+        <v>0.1842891532228128</v>
+      </c>
+      <c r="AF8" s="3" t="n">
+        <v>-0.02197221653629547</v>
+      </c>
+      <c r="AG8" s="3" t="n">
+        <v>0.04883749695674855</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="3" t="n">
+        <v>-6.938893903907228e-17</v>
+      </c>
+      <c r="AK8" s="3" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="3" t="n">
+        <v>0.02318587671251238</v>
+      </c>
+      <c r="AO8" s="3" t="n">
+        <v>0.04172379361860035</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>89</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T9" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="3" t="n">
+        <v>-0.06703406261266386</v>
+      </c>
+      <c r="AG9" s="3" t="n">
+        <v>0.2044491165694975</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-68</v>
+      </c>
+      <c r="AI9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" s="3" t="n">
+        <v>0.02318587671251238</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>-0.01772738840404031</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_wasserstein_gspc_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="M10" t="n">
+        <v>108</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="P10" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.06372707386676901</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.04506184607636839</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" s="3" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>34</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="AA10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>74</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="3" t="n">
+        <v>0.1842891532228128</v>
+      </c>
+      <c r="AF10" s="3" t="n">
+        <v>-0.02197221653629547</v>
+      </c>
+      <c r="AG10" s="3" t="n">
+        <v>0.04883749695674855</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="3" t="n">
+        <v>-6.938893903907228e-17</v>
+      </c>
+      <c r="AK10" s="3" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="3" t="n">
+        <v>0.02318587671251238</v>
+      </c>
+      <c r="AO10" s="3" t="n">
+        <v>0.04172379361860035</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10471,12 +11865,8 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>197</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>563</v>
-      </c>
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
@@ -10485,10 +11875,10 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="3" t="n">
-        <v>0.5562326869806095</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -10519,10 +11909,10 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>59</v>
+        <v>196</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>963</v>
+        <v>563</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -10532,7 +11922,7 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="3" t="n">
-        <v>0.9149709302325582</v>
+        <v>0.5568496949528563</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
@@ -10565,8 +11955,12 @@
           <t>C3</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>963</v>
+      </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
@@ -10575,10 +11969,10 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="3" t="n">
-        <v>0</v>
+        <v>0.9149709302325582</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -10651,24 +12045,20 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>-251</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>307</v>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" s="3" t="n">
-        <v>0.9766081871345029</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -10699,21 +12089,23 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-30</v>
-      </c>
-      <c r="F7" s="4" t="inlineStr"/>
+        <v>-251</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>307</v>
+      </c>
       <c r="G7" t="n">
-        <v>30</v>
+        <v>251</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" s="3" t="n">
+        <v>0.9766081871345029</v>
+      </c>
+      <c r="K7" t="n">
         <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -10730,30 +12122,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr"/>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>-30</v>
+      </c>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -10783,15 +12177,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>-43</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" t="n">
         <v>0</v>
       </c>
@@ -10800,10 +12190,10 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" s="3" t="n">
-        <v>0.3655523255813953</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -10830,7 +12220,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -10839,16 +12229,14 @@
         <v>0</v>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" s="3" t="n">
-        <v>0.5241379310344828</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -10875,11 +12263,15 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>-43</v>
+      </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
@@ -10888,10 +12280,10 @@
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" s="3" t="n">
-        <v>0</v>
+        <v>0.3655523255813953</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -10918,7 +12310,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -10930,13 +12322,13 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.4873294346978557</v>
+        <v>0.5205479452054794</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -10963,22 +12355,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>-30</v>
-      </c>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -10998,37 +12388,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>197</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>-193</v>
-      </c>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>57</v>
+      </c>
       <c r="J14" s="3" t="n">
-        <v>0.2770083102493075</v>
+        <v>0.4873294346978557</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -11045,37 +12433,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>209</v>
-      </c>
+        <v>-30</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" s="3" t="n">
-        <v>0.3670058139534884</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -11102,25 +12488,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>-134</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>339</v>
+      </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I16" t="n">
-        <v>6</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>0.5241379310344828</v>
-      </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -11147,11 +12535,15 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>196</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>-193</v>
+      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
@@ -11160,10 +12552,10 @@
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" s="3" t="n">
-        <v>0</v>
+        <v>0.2773155851358846</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -11190,14 +12582,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>307</v>
+        <v>209</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -11207,7 +12599,7 @@
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" s="3" t="n">
-        <v>0.9766081871345029</v>
+        <v>0.3670058139534884</v>
       </c>
       <c r="K18" t="n">
         <v>2</v>
@@ -11237,30 +12629,165 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>-30</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6</v>
+      </c>
       <c r="J19" s="3" t="n">
+        <v>0.5205479452054794</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>2</v>
       </c>
       <c r="M19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>307</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" s="3" t="n">
+        <v>0.9766081871345029</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>-30</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
